--- a/docs/planilha-atributos-cavalo-dre.xlsx
+++ b/docs/planilha-atributos-cavalo-dre.xlsx
@@ -129,7 +129,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -181,19 +181,37 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -573,7 +591,7 @@
     <col width="40" customWidth="1" min="2" max="2"/>
     <col width="95" customWidth="1" min="3" max="3"/>
     <col width="28" customWidth="1" min="4" max="4"/>
-    <col width="34" customWidth="1" min="5" max="5"/>
+    <col width="38" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -2678,7 +2696,7 @@
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="56" customWidth="1" min="4" max="4"/>
+    <col width="60" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2691,7 +2709,7 @@
     <row r="2" ht="46" customHeight="1">
       <c r="A2" s="17" t="inlineStr">
         <is>
-          <t>Sintético é a seção da DRE — a linha que totaliza. Analítico é a linha dentro dela: é sempre um detalhe do sintético da mesma coluna, nunca outra classificação. Um atributo tem exatamente um par sintético/analítico. Os seis sintéticos abaixo são a lista fechada; a coluna D da aba Atributos não aceita nada fora dela.</t>
+          <t>Sintético é a seção da DRE — a linha que totaliza. Analítico é a linha dentro dela: é sempre um detalhe do sintético da mesma coluna, nunca outra classificação. Um atributo tem exatamente um par sintético/analítico. Os seis sintéticos abaixo são a lista fechada, a mesma nas tabelas de cavalo e de implemento; a coluna D da aba Atributos não aceita nada fora dela.</t>
         </is>
       </c>
     </row>
@@ -2728,12 +2746,12 @@
           <t>Receita bruta</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C5" s="18" t="inlineStr">
         <is>
           <t>1.1</t>
         </is>
       </c>
-      <c r="D5" s="18" t="inlineStr">
+      <c r="D5" s="19" t="inlineStr">
         <is>
           <t>Remuneração fixa do cavalo</t>
         </is>
@@ -2750,12 +2768,12 @@
           <t>Receita bruta</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C6" s="18" t="inlineStr">
         <is>
           <t>1.2</t>
         </is>
       </c>
-      <c r="D6" s="18" t="inlineStr">
+      <c r="D6" s="19" t="inlineStr">
         <is>
           <t>Remuneração variável / produtividade (não confirmada — não soma)</t>
         </is>
@@ -2772,12 +2790,12 @@
           <t>(−) Deduções</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C7" s="20" t="inlineStr">
         <is>
           <t>2.1</t>
         </is>
       </c>
-      <c r="D7" s="19" t="inlineStr">
+      <c r="D7" s="21" t="inlineStr">
         <is>
           <t>ICMS sobre a prestação</t>
         </is>
@@ -2794,12 +2812,12 @@
           <t>(−) Custo variável</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C8" s="22" t="inlineStr">
         <is>
           <t>3.1</t>
         </is>
       </c>
-      <c r="D8" s="20" t="inlineStr">
+      <c r="D8" s="23" t="inlineStr">
         <is>
           <t>Combustível</t>
         </is>
@@ -2816,12 +2834,12 @@
           <t>(−) Custo variável</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="C9" s="22" t="inlineStr">
         <is>
           <t>3.2</t>
         </is>
       </c>
-      <c r="D9" s="20" t="inlineStr">
+      <c r="D9" s="23" t="inlineStr">
         <is>
           <t>Manutenção</t>
         </is>
@@ -2838,12 +2856,12 @@
           <t>(−) Custo variável</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="C10" s="22" t="inlineStr">
         <is>
           <t>3.3</t>
         </is>
       </c>
-      <c r="D10" s="20" t="inlineStr">
+      <c r="D10" s="23" t="inlineStr">
         <is>
           <t>Pneus</t>
         </is>
@@ -2860,12 +2878,12 @@
           <t>(−) Custo variável</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="C11" s="22" t="inlineStr">
         <is>
           <t>3.4</t>
         </is>
       </c>
-      <c r="D11" s="20" t="inlineStr">
+      <c r="D11" s="23" t="inlineStr">
         <is>
           <t>Outros</t>
         </is>
@@ -2882,12 +2900,12 @@
           <t>(−) Custo fixo</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="C12" s="24" t="inlineStr">
         <is>
           <t>4.1</t>
         </is>
       </c>
-      <c r="D12" s="21" t="inlineStr">
+      <c r="D12" s="25" t="inlineStr">
         <is>
           <t>IPVA e licenciamento</t>
         </is>
@@ -2904,12 +2922,12 @@
           <t>(−) Custo fixo</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
+      <c r="C13" s="24" t="inlineStr">
         <is>
           <t>4.2</t>
         </is>
       </c>
-      <c r="D13" s="21" t="inlineStr">
+      <c r="D13" s="25" t="inlineStr">
         <is>
           <t>Aluguel do veículo</t>
         </is>
@@ -2926,12 +2944,12 @@
           <t>(−) Depreciação e financeiro</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
+      <c r="C14" s="26" t="inlineStr">
         <is>
           <t>5.1</t>
         </is>
       </c>
-      <c r="D14" s="22" t="inlineStr">
+      <c r="D14" s="27" t="inlineStr">
         <is>
           <t>Amortização do principal (FINAME)</t>
         </is>
@@ -2948,12 +2966,12 @@
           <t>(−) Depreciação e financeiro</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
+      <c r="C15" s="26" t="inlineStr">
         <is>
           <t>5.2</t>
         </is>
       </c>
-      <c r="D15" s="22" t="inlineStr">
+      <c r="D15" s="27" t="inlineStr">
         <is>
           <t>Juros do FINAME</t>
         </is>
@@ -2970,12 +2988,12 @@
           <t>(−) Depreciação e financeiro</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
+      <c r="C16" s="26" t="inlineStr">
         <is>
           <t>5.3</t>
         </is>
       </c>
-      <c r="D16" s="22" t="inlineStr">
+      <c r="D16" s="27" t="inlineStr">
         <is>
           <t>Premissas do financiamento</t>
         </is>
@@ -2992,12 +3010,12 @@
           <t>Não entra na DRE</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
+      <c r="C17" s="28" t="inlineStr">
         <is>
           <t>9.1</t>
         </is>
       </c>
-      <c r="D17" s="23" t="inlineStr">
+      <c r="D17" s="29" t="inlineStr">
         <is>
           <t>Cadastral</t>
         </is>
@@ -3014,12 +3032,12 @@
           <t>Não entra na DRE</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
+      <c r="C18" s="28" t="inlineStr">
         <is>
           <t>9.2</t>
         </is>
       </c>
-      <c r="D18" s="23" t="inlineStr">
+      <c r="D18" s="29" t="inlineStr">
         <is>
           <t>Direcionador operacional</t>
         </is>
@@ -3036,19 +3054,19 @@
           <t>Não entra na DRE</t>
         </is>
       </c>
-      <c r="C19" s="2" t="inlineStr">
+      <c r="C19" s="28" t="inlineStr">
         <is>
           <t>9.3</t>
         </is>
       </c>
-      <c r="D19" s="23" t="inlineStr">
+      <c r="D19" s="29" t="inlineStr">
         <is>
           <t>Grandeza de aquisição (não entra na DRE do período)</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="60" customHeight="1">
-      <c r="A21" s="24" t="inlineStr">
+    <row r="21" ht="78" customHeight="1">
+      <c r="A21" s="30" t="inlineStr">
         <is>
           <t>As cinco primeiras seções e os seus componentes são os declarados em lib/dre/src/plano.ts (SECOES e PLANO_DA_DRE) — a autoridade da estrutura financeira no produto. O código 9 não é seção da DRE: reúne o que a planilha já marcava como fora dela (cadastro, direcionador operacional e grandeza de aquisição), agora com o motivo no analítico. As colunas Atributo, Nome Gerencial e O que é não foram alteradas.</t>
         </is>

--- a/docs/planilha-atributos-cavalo-dre.xlsx
+++ b/docs/planilha-atributos-cavalo-dre.xlsx
@@ -2677,7 +2677,7 @@
   <autoFilter ref="A1:E77"/>
   <dataValidations count="1">
     <dataValidation sqref="D2:D77" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="Categoria DRE - Sintético" error="Use um dos seis sintéticos da aba Categorias DRE." type="list">
-      <formula1>"Receita bruta,(−) Deduções,(−) Custo variável,(−) Custo fixo,(−) Depreciação e financeiro,Não entra na DRE"</formula1>
+      <formula1>"Receita bruta,(−) Deduções,(−) Custo variável,(−) Custo fixo,(−) Depreciação e financeiro,Subtotal e margem,Não entra na DRE"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
